--- a/DesignTable/Data/Table/Tables/projectile.xlsx
+++ b/DesignTable/Data/Table/Tables/projectile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E0971E-D123-4B82-8D17-A53FAF80AFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F75CAE98-CDB4-409C-A0B7-4761278A5270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{88BC60B1-E75D-49F4-A27E-77A81F2A3ACA}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88BC60B1-E75D-49F4-A27E-77A81F2A3ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>projectile_Id</t>
   </si>
   <si>
@@ -113,6 +109,14 @@
   </si>
   <si>
     <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +174,10 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -195,7 +202,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="projectile">
         <xsd:complexType>
@@ -210,6 +217,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -227,7 +235,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="projectile_맵" RootElement="projectile" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -235,14 +243,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E1FE1C17-2501-4D71-A9F2-E6CFD797235B}" name="표2" displayName="표2" ref="A1:C2" tableType="xml" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{E1FE1C17-2501-4D71-A9F2-E6CFD797235B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62C4B69E-C89A-48C3-9F4E-C8F19119D08C}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="2">
-      <xmlColumnPr mapId="1" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{4F2C4396-12A7-447A-8A7D-727306916570}" uniqueName="projectile_path" name="projectile_path" dataDxfId="1">
-      <xmlColumnPr mapId="1" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{F60FE2EC-9B96-432D-BA58-2B732DF3674C}" uniqueName="projectile_speed" name="projectile_speed" dataDxfId="0">
-      <xmlColumnPr mapId="1" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
+    <tableColumn id="1" xr3:uid="{62C4B69E-C89A-48C3-9F4E-C8F19119D08C}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="3">
+      <xmlColumnPr mapId="4" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{4F2C4396-12A7-447A-8A7D-727306916570}" uniqueName="projectile_path" name="projectile_path" dataDxfId="2">
+      <xmlColumnPr mapId="4" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{F60FE2EC-9B96-432D-BA58-2B732DF3674C}" uniqueName="projectile_speed" name="projectile_speed" dataDxfId="1">
+      <xmlColumnPr mapId="4" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -250,35 +258,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}" name="표1" displayName="표1" ref="A1:I4" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I4" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}" name="표1" displayName="표1" ref="A1:J4" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J4" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CF6E2B9A-C78F-4CBD-AA10-C6FBFBB1E147}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{5D174F7B-C4F0-46D9-88B7-5D56C162E343}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{89897B77-71BF-4633-A346-566BD19C47B1}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9E19B0B4-13E5-4998-834B-1D06B8493818}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{1B288A30-7414-43EC-8164-2D7D1E8B7DFF}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{5C4F6795-2111-4949-9758-65383DD33F2B}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{7F3352C5-5EE0-4234-9E51-DDD7BC14FDB4}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87B4F343-178C-4B54-AE7D-C37927F2FBCC}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{420E4748-CCE1-4823-9359-034EE2EDDC7B}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{420E4748-CCE1-4823-9359-034EE2EDDC7B}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{006FEEE5-7398-419E-84D6-CD786487B892}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -590,24 +601,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -621,10 +632,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BC88B-03C1-40BC-A9AE-8D76F735343D}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,93 +661,105 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1022</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1022</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
         <v>1022</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/projectile.xlsx
+++ b/DesignTable/Data/Table/Tables/projectile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F75CAE98-CDB4-409C-A0B7-4761278A5270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DFC51B6-CEE0-4EEB-A34B-45D2E0297043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88BC60B1-E75D-49F4-A27E-77A81F2A3ACA}"/>
   </bookViews>
@@ -235,7 +235,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -244,13 +244,13 @@
   <autoFilter ref="A1:C2" xr:uid="{E1FE1C17-2501-4D71-A9F2-E6CFD797235B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{62C4B69E-C89A-48C3-9F4E-C8F19119D08C}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="3">
-      <xmlColumnPr mapId="4" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4F2C4396-12A7-447A-8A7D-727306916570}" uniqueName="projectile_path" name="projectile_path" dataDxfId="2">
-      <xmlColumnPr mapId="4" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F60FE2EC-9B96-432D-BA58-2B732DF3674C}" uniqueName="projectile_speed" name="projectile_speed" dataDxfId="1">
-      <xmlColumnPr mapId="4" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -262,34 +262,34 @@
   <autoFilter ref="A1:J4" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CF6E2B9A-C78F-4CBD-AA10-C6FBFBB1E147}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{5D174F7B-C4F0-46D9-88B7-5D56C162E343}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{89897B77-71BF-4633-A346-566BD19C47B1}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9E19B0B4-13E5-4998-834B-1D06B8493818}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{1B288A30-7414-43EC-8164-2D7D1E8B7DFF}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{5C4F6795-2111-4949-9758-65383DD33F2B}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{7F3352C5-5EE0-4234-9E51-DDD7BC14FDB4}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87B4F343-178C-4B54-AE7D-C37927F2FBCC}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{420E4748-CCE1-4823-9359-034EE2EDDC7B}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{006FEEE5-7398-419E-84D6-CD786487B892}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/projectile.xlsx
+++ b/DesignTable/Data/Table/Tables/projectile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DFC51B6-CEE0-4EEB-A34B-45D2E0297043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{932F0CAB-D7F8-4252-96E5-A513C295805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88BC60B1-E75D-49F4-A27E-77A81F2A3ACA}"/>
   </bookViews>
@@ -235,7 +235,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -244,13 +244,13 @@
   <autoFilter ref="A1:C2" xr:uid="{E1FE1C17-2501-4D71-A9F2-E6CFD797235B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{62C4B69E-C89A-48C3-9F4E-C8F19119D08C}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="3">
-      <xmlColumnPr mapId="6" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4F2C4396-12A7-447A-8A7D-727306916570}" uniqueName="projectile_path" name="projectile_path" dataDxfId="2">
-      <xmlColumnPr mapId="6" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F60FE2EC-9B96-432D-BA58-2B732DF3674C}" uniqueName="projectile_speed" name="projectile_speed" dataDxfId="1">
-      <xmlColumnPr mapId="6" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -262,34 +262,34 @@
   <autoFilter ref="A1:J4" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CF6E2B9A-C78F-4CBD-AA10-C6FBFBB1E147}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{5D174F7B-C4F0-46D9-88B7-5D56C162E343}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{89897B77-71BF-4633-A346-566BD19C47B1}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9E19B0B4-13E5-4998-834B-1D06B8493818}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{1B288A30-7414-43EC-8164-2D7D1E8B7DFF}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{5C4F6795-2111-4949-9758-65383DD33F2B}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{7F3352C5-5EE0-4234-9E51-DDD7BC14FDB4}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87B4F343-178C-4B54-AE7D-C37927F2FBCC}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{420E4748-CCE1-4823-9359-034EE2EDDC7B}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{006FEEE5-7398-419E-84D6-CD786487B892}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/projectile.xlsx
+++ b/DesignTable/Data/Table/Tables/projectile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{932F0CAB-D7F8-4252-96E5-A513C295805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{159C4A5B-B936-4876-B815-C48941A9AFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88BC60B1-E75D-49F4-A27E-77A81F2A3ACA}"/>
   </bookViews>
@@ -235,7 +235,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="projectile_맵" RootElement="projectile" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -244,13 +244,13 @@
   <autoFilter ref="A1:C2" xr:uid="{E1FE1C17-2501-4D71-A9F2-E6CFD797235B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{62C4B69E-C89A-48C3-9F4E-C8F19119D08C}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="3">
-      <xmlColumnPr mapId="8" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/record/projectile_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4F2C4396-12A7-447A-8A7D-727306916570}" uniqueName="projectile_path" name="projectile_path" dataDxfId="2">
-      <xmlColumnPr mapId="8" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/record/projectile_path" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F60FE2EC-9B96-432D-BA58-2B732DF3674C}" uniqueName="projectile_speed" name="projectile_speed" dataDxfId="1">
-      <xmlColumnPr mapId="8" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/record/projectile_speed" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -262,34 +262,34 @@
   <autoFilter ref="A1:J4" xr:uid="{DBF12000-1CFE-47FD-8466-39E376EF19F3}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CF6E2B9A-C78F-4CBD-AA10-C6FBFBB1E147}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{5D174F7B-C4F0-46D9-88B7-5D56C162E343}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{89897B77-71BF-4633-A346-566BD19C47B1}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9E19B0B4-13E5-4998-834B-1D06B8493818}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{1B288A30-7414-43EC-8164-2D7D1E8B7DFF}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{5C4F6795-2111-4949-9758-65383DD33F2B}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{7F3352C5-5EE0-4234-9E51-DDD7BC14FDB4}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{87B4F343-178C-4B54-AE7D-C37927F2FBCC}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{420E4748-CCE1-4823-9359-034EE2EDDC7B}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{006FEEE5-7398-419E-84D6-CD786487B892}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/projectile/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
